--- a/calendar_chilean_2024A.xlsx
+++ b/calendar_chilean_2024A.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ed268546/Dropbox/Mac/Documents/codes/SPOCK_chilean/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41003780-1EDA-6B4C-B136-E981DFEFFC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7256286-6B95-054C-BAAE-47E3100E0D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1020" windowWidth="35840" windowHeight="20840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="34">
   <si>
     <t>Date</t>
   </si>
@@ -135,6 +135,9 @@
   <si>
     <t/>
   </si>
+  <si>
+    <t>check</t>
+  </si>
 </sst>
 </file>
 
@@ -174,7 +177,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -221,6 +224,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFBD2FF"/>
         <bgColor rgb="FFFBD2FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -860,7 +869,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1018,6 +1027,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4331,7 +4343,7 @@
       <c r="G120" s="50"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10"/>
-      <c r="J120" s="52"/>
+      <c r="J120" s="51"/>
     </row>
     <row r="121" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="34">
@@ -4359,7 +4371,9 @@
         <v>20</v>
       </c>
       <c r="I121" s="10"/>
-      <c r="J121" s="51"/>
+      <c r="J121" s="61" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="122" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="34">
@@ -4387,7 +4401,9 @@
         <v>20</v>
       </c>
       <c r="I122" s="10"/>
-      <c r="J122" s="51"/>
+      <c r="J122" s="51" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="123" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="34">
@@ -4415,7 +4431,9 @@
         <v>20</v>
       </c>
       <c r="I123" s="10"/>
-      <c r="J123" s="51"/>
+      <c r="J123" s="51" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="124" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="34">
@@ -4553,7 +4571,9 @@
         <v>20</v>
       </c>
       <c r="I129" s="10"/>
-      <c r="J129" s="51"/>
+      <c r="J129" s="51" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="130" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="34">
@@ -4581,7 +4601,9 @@
         <v>20</v>
       </c>
       <c r="I130" s="10"/>
-      <c r="J130" s="51"/>
+      <c r="J130" s="51" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="131" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="34">
@@ -4609,7 +4631,9 @@
         <v>20</v>
       </c>
       <c r="I131" s="10"/>
-      <c r="J131" s="51"/>
+      <c r="J131" s="51" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="132" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="34">
@@ -4747,7 +4771,9 @@
         <v>20</v>
       </c>
       <c r="I137" s="10"/>
-      <c r="J137" s="51"/>
+      <c r="J137" s="61" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="138" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="34">
@@ -4775,7 +4801,9 @@
         <v>20</v>
       </c>
       <c r="I138" s="10"/>
-      <c r="J138" s="51"/>
+      <c r="J138" s="51" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="139" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="34">
@@ -4803,7 +4831,9 @@
         <v>20</v>
       </c>
       <c r="I139" s="10"/>
-      <c r="J139" s="51"/>
+      <c r="J139" s="51" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="140" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="34">
@@ -4941,7 +4971,9 @@
         <v>20</v>
       </c>
       <c r="I145" s="10"/>
-      <c r="J145" s="51"/>
+      <c r="J145" s="51" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="146" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A146" s="34">
@@ -4969,7 +5001,9 @@
         <v>20</v>
       </c>
       <c r="I146" s="10"/>
-      <c r="J146" s="51"/>
+      <c r="J146" s="51" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="147" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="34">
@@ -4997,7 +5031,9 @@
         <v>20</v>
       </c>
       <c r="I147" s="10"/>
-      <c r="J147" s="51"/>
+      <c r="J147" s="51" t="s">
+        <v>20</v>
+      </c>
       <c r="L147" s="13" t="s">
         <v>14</v>
       </c>
@@ -5174,7 +5210,9 @@
         <v>20</v>
       </c>
       <c r="I153" s="10"/>
-      <c r="J153" s="51"/>
+      <c r="J153" s="61" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="154" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="34">
@@ -5202,7 +5240,9 @@
         <v>20</v>
       </c>
       <c r="I154" s="10"/>
-      <c r="J154" s="52"/>
+      <c r="J154" s="61" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="155" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="34">
@@ -5230,7 +5270,9 @@
         <v>20</v>
       </c>
       <c r="I155" s="10"/>
-      <c r="J155" s="52"/>
+      <c r="J155" s="51" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="156" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="34">
@@ -5368,7 +5410,9 @@
         <v>20</v>
       </c>
       <c r="I161" s="10"/>
-      <c r="J161" s="52"/>
+      <c r="J161" s="51" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="162" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="34">
@@ -5396,7 +5440,9 @@
         <v>20</v>
       </c>
       <c r="I162" s="10"/>
-      <c r="J162" s="52"/>
+      <c r="J162" s="51" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="163" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="34">
@@ -5554,9 +5600,13 @@
       <c r="G169" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="H169" s="9"/>
+      <c r="H169" s="9" t="s">
+        <v>20</v>
+      </c>
       <c r="I169" s="10"/>
-      <c r="J169" s="52"/>
+      <c r="J169" s="51" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="170" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="34">
@@ -5580,9 +5630,13 @@
       <c r="G170" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="H170" s="9"/>
+      <c r="H170" s="9" t="s">
+        <v>20</v>
+      </c>
       <c r="I170" s="10"/>
-      <c r="J170" s="52"/>
+      <c r="J170" s="51" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="171" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="34">
@@ -5735,10 +5789,14 @@
       <c r="F177" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="G177" s="50"/>
+      <c r="G177" s="50" t="s">
+        <v>20</v>
+      </c>
       <c r="H177" s="9"/>
       <c r="I177" s="10"/>
-      <c r="J177" s="52"/>
+      <c r="J177" s="61" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="178" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="34">
@@ -5759,10 +5817,14 @@
       <c r="F178" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="G178" s="50"/>
+      <c r="G178" s="50" t="s">
+        <v>20</v>
+      </c>
       <c r="H178" s="9"/>
       <c r="I178" s="10"/>
-      <c r="J178" s="52"/>
+      <c r="J178" s="61" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="179" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="34">
@@ -5925,7 +5987,7 @@
       <c r="I185" s="24"/>
       <c r="J185" s="45">
         <f>COUNTIF(J1:J184,"True")</f>
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/calendar_chilean_2024A.xlsx
+++ b/calendar_chilean_2024A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ed268546/Dropbox/Mac/Documents/codes/SPOCK_chilean/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7256286-6B95-054C-BAAE-47E3100E0D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51168FD3-F764-0640-8DCB-C19F6BE1C53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1020" windowWidth="35840" windowHeight="20840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="35840" windowHeight="20840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="36">
   <si>
     <t>Date</t>
   </si>
@@ -118,9 +118,6 @@
     <t>pb plans, wind</t>
   </si>
   <si>
-    <t>to check</t>
-  </si>
-  <si>
     <t xml:space="preserve"> catch up Shablovinskaya</t>
   </si>
   <si>
@@ -136,7 +133,16 @@
     <t/>
   </si>
   <si>
-    <t>check</t>
+    <t>pb_plans</t>
+  </si>
+  <si>
+    <t>strong wind</t>
+  </si>
+  <si>
+    <t>cloud and wind</t>
+  </si>
+  <si>
+    <t>nothing on ESO bit of wind</t>
   </si>
 </sst>
 </file>
@@ -177,7 +183,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -224,12 +230,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFBD2FF"/>
         <bgColor rgb="FFFBD2FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1029,14 +1029,94 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1715,7 +1795,7 @@
       <c r="I16" s="10"/>
       <c r="J16" s="52"/>
     </row>
-    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="34">
         <v>45398</v>
       </c>
@@ -1737,7 +1817,7 @@
       <c r="I17" s="10"/>
       <c r="J17" s="52"/>
     </row>
-    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="34">
         <v>45399</v>
       </c>
@@ -1767,7 +1847,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="34">
         <v>45400</v>
       </c>
@@ -1797,7 +1877,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="34">
         <v>45401</v>
       </c>
@@ -1823,11 +1903,14 @@
         <v>20</v>
       </c>
       <c r="I20" s="10"/>
-      <c r="J20" s="51" t="s">
+      <c r="J20" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" s="51" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="34">
         <v>45402</v>
       </c>
@@ -1849,7 +1932,7 @@
       <c r="I21" s="10"/>
       <c r="J21" s="51"/>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="34">
         <v>45403</v>
       </c>
@@ -1871,7 +1954,7 @@
       <c r="I22" s="10"/>
       <c r="J22" s="51"/>
     </row>
-    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="34">
         <v>45404</v>
       </c>
@@ -1893,7 +1976,7 @@
       <c r="I23" s="10"/>
       <c r="J23" s="52"/>
     </row>
-    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="34">
         <v>45405</v>
       </c>
@@ -1915,7 +1998,7 @@
       <c r="I24" s="10"/>
       <c r="J24" s="52"/>
     </row>
-    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="34">
         <v>45406</v>
       </c>
@@ -1937,7 +2020,7 @@
       <c r="I25" s="10"/>
       <c r="J25" s="52"/>
     </row>
-    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="34">
         <v>45407</v>
       </c>
@@ -1967,7 +2050,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="34">
         <v>45408</v>
       </c>
@@ -1997,7 +2080,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="34">
         <v>45409</v>
       </c>
@@ -2027,7 +2110,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="34">
         <v>45410</v>
       </c>
@@ -2044,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G29" s="50" t="s">
         <v>20</v>
@@ -2053,11 +2136,14 @@
         <v>20</v>
       </c>
       <c r="I29" s="10"/>
-      <c r="J29" s="51" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J29" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="K29" s="61" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="34">
         <v>45411</v>
       </c>
@@ -2079,7 +2165,7 @@
       <c r="I30" s="10"/>
       <c r="J30" s="51"/>
     </row>
-    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="34">
         <v>45412</v>
       </c>
@@ -2101,7 +2187,7 @@
       <c r="I31" s="10"/>
       <c r="J31" s="51"/>
     </row>
-    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="34">
         <v>45413</v>
       </c>
@@ -2123,7 +2209,7 @@
       <c r="I32" s="10"/>
       <c r="J32" s="52"/>
     </row>
-    <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="34">
         <v>45414</v>
       </c>
@@ -2145,7 +2231,7 @@
       <c r="I33" s="10"/>
       <c r="J33" s="52"/>
     </row>
-    <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="34">
         <v>45415</v>
       </c>
@@ -2171,11 +2257,14 @@
         <v>22</v>
       </c>
       <c r="I34" s="9"/>
-      <c r="J34" s="51" t="s">
+      <c r="J34" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="K34" s="51" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="34">
         <v>45416</v>
       </c>
@@ -2201,11 +2290,14 @@
         <v>20</v>
       </c>
       <c r="I35" s="10"/>
-      <c r="J35" s="51" t="s">
+      <c r="J35" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="K35" s="51" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="34">
         <v>45417</v>
       </c>
@@ -2231,11 +2323,14 @@
         <v>20</v>
       </c>
       <c r="I36" s="10"/>
-      <c r="J36" s="51" t="s">
+      <c r="J36" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="K36" s="51" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="34">
         <v>45418</v>
       </c>
@@ -2257,7 +2352,7 @@
       <c r="I37" s="10"/>
       <c r="J37" s="51"/>
     </row>
-    <row r="38" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="34">
         <v>45419</v>
       </c>
@@ -2279,7 +2374,7 @@
       <c r="I38" s="10"/>
       <c r="J38" s="51"/>
     </row>
-    <row r="39" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="34">
         <v>45420</v>
       </c>
@@ -2301,7 +2396,7 @@
       <c r="I39" s="10"/>
       <c r="J39" s="51"/>
     </row>
-    <row r="40" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="34">
         <v>45421</v>
       </c>
@@ -2323,7 +2418,7 @@
       <c r="I40" s="10"/>
       <c r="J40" s="51"/>
     </row>
-    <row r="41" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="34">
         <v>45422</v>
       </c>
@@ -2345,7 +2440,7 @@
       <c r="I41" s="10"/>
       <c r="J41" s="52"/>
     </row>
-    <row r="42" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="34">
         <v>45423</v>
       </c>
@@ -2375,7 +2470,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="34">
         <v>45424</v>
       </c>
@@ -2405,7 +2500,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="34">
         <v>45425</v>
       </c>
@@ -2435,7 +2530,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="34">
         <v>45426</v>
       </c>
@@ -2457,7 +2552,7 @@
       <c r="I45" s="10"/>
       <c r="J45" s="52"/>
     </row>
-    <row r="46" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="34">
         <v>45427</v>
       </c>
@@ -2479,7 +2574,7 @@
       <c r="I46" s="10"/>
       <c r="J46" s="52"/>
     </row>
-    <row r="47" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="34">
         <v>45428</v>
       </c>
@@ -2501,7 +2596,7 @@
       <c r="I47" s="10"/>
       <c r="J47" s="51"/>
     </row>
-    <row r="48" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="34">
         <v>45429</v>
       </c>
@@ -2523,7 +2618,7 @@
       <c r="I48" s="10"/>
       <c r="J48" s="51"/>
     </row>
-    <row r="49" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="34">
         <v>45430</v>
       </c>
@@ -2545,7 +2640,7 @@
       <c r="I49" s="10"/>
       <c r="J49" s="51"/>
     </row>
-    <row r="50" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="34">
         <v>45431</v>
       </c>
@@ -2571,11 +2666,14 @@
         <v>20</v>
       </c>
       <c r="I50" s="10"/>
-      <c r="J50" s="52" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J50" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="K50" s="52" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="34">
         <v>45432</v>
       </c>
@@ -2601,11 +2699,14 @@
         <v>20</v>
       </c>
       <c r="I51" s="10"/>
-      <c r="J51" s="52" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J51" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="K51" s="52" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="34">
         <v>45433</v>
       </c>
@@ -2625,7 +2726,7 @@
         <v>10</v>
       </c>
       <c r="G52" s="54" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H52" s="27" t="s">
         <v>22</v>
@@ -2635,7 +2736,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="34">
         <v>45434</v>
       </c>
@@ -2657,7 +2758,7 @@
       <c r="I53" s="10"/>
       <c r="J53" s="52"/>
     </row>
-    <row r="54" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="34">
         <v>45435</v>
       </c>
@@ -2679,7 +2780,7 @@
       <c r="I54" s="10"/>
       <c r="J54" s="52"/>
     </row>
-    <row r="55" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="34">
         <v>45436</v>
       </c>
@@ -2701,7 +2802,7 @@
       <c r="I55" s="10"/>
       <c r="J55" s="52"/>
     </row>
-    <row r="56" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="34">
         <v>45437</v>
       </c>
@@ -2723,7 +2824,7 @@
       <c r="I56" s="10"/>
       <c r="J56" s="51"/>
     </row>
-    <row r="57" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="34">
         <v>45438</v>
       </c>
@@ -2745,7 +2846,7 @@
       <c r="I57" s="10"/>
       <c r="J57" s="51"/>
     </row>
-    <row r="58" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="34">
         <v>45439</v>
       </c>
@@ -2771,11 +2872,14 @@
         <v>20</v>
       </c>
       <c r="I58" s="10"/>
-      <c r="J58" s="52" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J58" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="K58" s="52" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="34">
         <v>45440</v>
       </c>
@@ -2801,11 +2905,14 @@
         <v>20</v>
       </c>
       <c r="I59" s="10"/>
-      <c r="J59" s="52" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J59" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="K59" s="52" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="34">
         <v>45441</v>
       </c>
@@ -2825,7 +2932,7 @@
         <v>10</v>
       </c>
       <c r="G60" s="54" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H60" s="27" t="s">
         <v>22</v>
@@ -2835,7 +2942,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="34">
         <v>45442</v>
       </c>
@@ -2857,7 +2964,7 @@
       <c r="I61" s="10"/>
       <c r="J61" s="52"/>
     </row>
-    <row r="62" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="34">
         <v>45443</v>
       </c>
@@ -2879,7 +2986,7 @@
       <c r="I62" s="10"/>
       <c r="J62" s="52"/>
     </row>
-    <row r="63" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="34">
         <v>45444</v>
       </c>
@@ -2901,7 +3008,7 @@
       <c r="I63" s="10"/>
       <c r="J63" s="52"/>
     </row>
-    <row r="64" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="34">
         <v>45445</v>
       </c>
@@ -3738,7 +3845,7 @@
       <c r="I96" s="10"/>
       <c r="J96" s="52"/>
     </row>
-    <row r="97" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="34">
         <v>45478</v>
       </c>
@@ -3767,8 +3874,11 @@
       <c r="J97" s="55" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="98" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K97" s="61" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="34">
         <v>45479</v>
       </c>
@@ -3798,7 +3908,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="34">
         <v>45480</v>
       </c>
@@ -3828,7 +3938,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="34">
         <v>45481</v>
       </c>
@@ -3850,7 +3960,7 @@
       <c r="I100" s="10"/>
       <c r="J100" s="52"/>
     </row>
-    <row r="101" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="34">
         <v>45482</v>
       </c>
@@ -3872,7 +3982,7 @@
       <c r="I101" s="10"/>
       <c r="J101" s="52"/>
     </row>
-    <row r="102" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="34">
         <v>45483</v>
       </c>
@@ -3894,7 +4004,7 @@
       <c r="I102" s="10"/>
       <c r="J102" s="52"/>
     </row>
-    <row r="103" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="34">
         <v>45484</v>
       </c>
@@ -3916,7 +4026,7 @@
       <c r="I103" s="10"/>
       <c r="J103" s="52"/>
     </row>
-    <row r="104" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="34">
         <v>45485</v>
       </c>
@@ -3938,7 +4048,7 @@
       <c r="I104" s="10"/>
       <c r="J104" s="52"/>
     </row>
-    <row r="105" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="34">
         <v>45486</v>
       </c>
@@ -3968,7 +4078,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="34">
         <v>45487</v>
       </c>
@@ -3998,7 +4108,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="34">
         <v>45488</v>
       </c>
@@ -4028,7 +4138,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="34">
         <v>45489</v>
       </c>
@@ -4050,7 +4160,7 @@
       <c r="I108" s="10"/>
       <c r="J108" s="52"/>
     </row>
-    <row r="109" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="34">
         <v>45490</v>
       </c>
@@ -4072,7 +4182,7 @@
       <c r="I109" s="10"/>
       <c r="J109" s="52"/>
     </row>
-    <row r="110" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="34">
         <v>45491</v>
       </c>
@@ -4094,7 +4204,7 @@
       <c r="I110" s="10"/>
       <c r="J110" s="52"/>
     </row>
-    <row r="111" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="34">
         <v>45492</v>
       </c>
@@ -4116,7 +4226,7 @@
       <c r="I111" s="10"/>
       <c r="J111" s="52"/>
     </row>
-    <row r="112" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="34">
         <v>45493</v>
       </c>
@@ -4168,7 +4278,7 @@
         <v>22</v>
       </c>
       <c r="K113" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4201,7 +4311,7 @@
         <v>22</v>
       </c>
       <c r="K114" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4371,8 +4481,11 @@
         <v>20</v>
       </c>
       <c r="I121" s="10"/>
-      <c r="J121" s="61" t="s">
-        <v>33</v>
+      <c r="J121" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="K121" s="61" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4545,7 +4658,7 @@
       <c r="I128" s="10"/>
       <c r="J128" s="52"/>
     </row>
-    <row r="129" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="34">
         <v>45510</v>
       </c>
@@ -4575,7 +4688,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="34">
         <v>45511</v>
       </c>
@@ -4605,7 +4718,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="34">
         <v>45512</v>
       </c>
@@ -4635,7 +4748,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="34">
         <v>45513</v>
       </c>
@@ -4657,7 +4770,7 @@
       <c r="I132" s="10"/>
       <c r="J132" s="52"/>
     </row>
-    <row r="133" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="34">
         <v>45514</v>
       </c>
@@ -4679,7 +4792,7 @@
       <c r="I133" s="10"/>
       <c r="J133" s="52"/>
     </row>
-    <row r="134" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="34">
         <v>45515</v>
       </c>
@@ -4701,7 +4814,7 @@
       <c r="I134" s="10"/>
       <c r="J134" s="52"/>
     </row>
-    <row r="135" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="34">
         <v>45516</v>
       </c>
@@ -4723,7 +4836,7 @@
       <c r="I135" s="10"/>
       <c r="J135" s="52"/>
     </row>
-    <row r="136" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="34">
         <v>45517</v>
       </c>
@@ -4745,7 +4858,7 @@
       <c r="I136" s="10"/>
       <c r="J136" s="52"/>
     </row>
-    <row r="137" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="34">
         <v>45518</v>
       </c>
@@ -4771,11 +4884,14 @@
         <v>20</v>
       </c>
       <c r="I137" s="10"/>
-      <c r="J137" s="61" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J137" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="K137" s="61" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="34">
         <v>45519</v>
       </c>
@@ -4805,7 +4921,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="34">
         <v>45520</v>
       </c>
@@ -4835,7 +4951,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="34">
         <v>45521</v>
       </c>
@@ -4857,7 +4973,7 @@
       <c r="I140" s="10"/>
       <c r="J140" s="52"/>
     </row>
-    <row r="141" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="34">
         <v>45522</v>
       </c>
@@ -4879,7 +4995,7 @@
       <c r="I141" s="10"/>
       <c r="J141" s="52"/>
     </row>
-    <row r="142" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="34">
         <v>45523</v>
       </c>
@@ -4901,7 +5017,7 @@
       <c r="I142" s="10"/>
       <c r="J142" s="52"/>
     </row>
-    <row r="143" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="34">
         <v>45524</v>
       </c>
@@ -4923,7 +5039,7 @@
       <c r="I143" s="10"/>
       <c r="J143" s="52"/>
     </row>
-    <row r="144" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="34">
         <v>45525</v>
       </c>
@@ -5210,8 +5326,11 @@
         <v>20</v>
       </c>
       <c r="I153" s="10"/>
-      <c r="J153" s="61" t="s">
-        <v>33</v>
+      <c r="J153" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="K153" s="61" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="154" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5240,8 +5359,11 @@
         <v>20</v>
       </c>
       <c r="I154" s="10"/>
-      <c r="J154" s="61" t="s">
-        <v>33</v>
+      <c r="J154" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="K154" s="61" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="155" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5463,7 +5585,7 @@
       <c r="F163" s="38"/>
       <c r="G163" s="50"/>
       <c r="H163" s="60" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I163" s="10"/>
       <c r="J163" s="52"/>
@@ -5770,7 +5892,7 @@
       <c r="I176" s="10"/>
       <c r="J176" s="52"/>
     </row>
-    <row r="177" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="34">
         <v>45558</v>
       </c>
@@ -5794,11 +5916,14 @@
       </c>
       <c r="H177" s="9"/>
       <c r="I177" s="10"/>
-      <c r="J177" s="61" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="178" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J177" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="K177" s="61" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="34">
         <v>45559</v>
       </c>
@@ -5822,11 +5947,11 @@
       </c>
       <c r="H178" s="9"/>
       <c r="I178" s="10"/>
-      <c r="J178" s="61" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="179" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J178" s="50" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="34">
         <v>45560</v>
       </c>
@@ -5848,7 +5973,7 @@
       <c r="I179" s="10"/>
       <c r="J179" s="52"/>
     </row>
-    <row r="180" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="34">
         <v>45561</v>
       </c>
@@ -5870,7 +5995,7 @@
       <c r="I180" s="10"/>
       <c r="J180" s="52"/>
     </row>
-    <row r="181" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="34">
         <v>45562</v>
       </c>
@@ -5892,7 +6017,7 @@
       <c r="I181" s="10"/>
       <c r="J181" s="52"/>
     </row>
-    <row r="182" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="34">
         <v>45563</v>
       </c>
@@ -5914,7 +6039,7 @@
       <c r="I182" s="10"/>
       <c r="J182" s="52"/>
     </row>
-    <row r="183" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="34">
         <v>45564</v>
       </c>
@@ -5936,7 +6061,7 @@
       <c r="I183" s="10"/>
       <c r="J183" s="52"/>
     </row>
-    <row r="184" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A184" s="35">
         <v>45565</v>
       </c>
@@ -5958,7 +6083,7 @@
       <c r="I184" s="58"/>
       <c r="J184" s="59"/>
     </row>
-    <row r="185" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A185" s="32" t="s">
         <v>19</v>
       </c>
@@ -5987,24 +6112,56 @@
       <c r="I185" s="24"/>
       <c r="J185" s="45">
         <f>COUNTIF(J1:J184,"True")</f>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G1:J113 K74:K75 K113 G114:K115 G116:J184">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="False">
+  <conditionalFormatting sqref="K74:K75 K113 G114:K115 K29 G1:J113 K97 J121:K121 J137:K137 K153:K154 G116:J184 K177">
+    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="False">
       <formula>NOT(ISERROR(SEARCH("False",G1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" stopIfTrue="1" operator="containsText" text="True">
+    <cfRule type="containsText" dxfId="10" priority="12" stopIfTrue="1" operator="containsText" text="True">
       <formula>NOT(ISERROR(SEARCH("True",G1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K81:K83">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="False">
+    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="False">
       <formula>NOT(ISERROR(SEARCH("False",K81)))</formula>
     </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="10" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",K81)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K34:K36">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="False">
+      <formula>NOT(ISERROR(SEARCH("False",K34)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="8" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",K34)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K20">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="False">
+      <formula>NOT(ISERROR(SEARCH("False",K20)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="6" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",K20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K50:K51">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="False">
+      <formula>NOT(ISERROR(SEARCH("False",K50)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="4" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",K50)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K58:K59">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="False">
+      <formula>NOT(ISERROR(SEARCH("False",K58)))</formula>
+    </cfRule>
     <cfRule type="containsText" dxfId="0" priority="2" stopIfTrue="1" operator="containsText" text="True">
-      <formula>NOT(ISERROR(SEARCH("True",K81)))</formula>
+      <formula>NOT(ISERROR(SEARCH("True",K58)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
